--- a/src/test/resources/importBangQuyDoi.xlsx
+++ b/src/test/resources/importBangQuyDoi.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="388">
   <si>
     <t>idqd</t>
   </si>
@@ -392,160 +392,661 @@
     <t>VSAT</t>
   </si>
   <si>
-    <t>6.67</t>
-  </si>
-  <si>
-    <t>9.93</t>
-  </si>
-  <si>
-    <t>VSAT_A00_1</t>
-  </si>
-  <si>
-    <t>13.27</t>
-  </si>
-  <si>
-    <t>VSAT_A00_2</t>
-  </si>
-  <si>
-    <t>13.33</t>
-  </si>
-  <si>
-    <t>16.60</t>
-  </si>
-  <si>
-    <t>VSAT_A00_3</t>
-  </si>
-  <si>
-    <t>16.67</t>
-  </si>
-  <si>
-    <t>19.93</t>
-  </si>
-  <si>
-    <t>VSAT_A00_4</t>
-  </si>
-  <si>
-    <t>23.27</t>
-  </si>
-  <si>
-    <t>VSAT_A00_5</t>
-  </si>
-  <si>
-    <t>23.33</t>
-  </si>
-  <si>
-    <t>26.60</t>
-  </si>
-  <si>
-    <t>VSAT_A00_6</t>
-  </si>
-  <si>
-    <t>26.67</t>
-  </si>
-  <si>
-    <t>27.93</t>
-  </si>
-  <si>
-    <t>VSAT_A00_7</t>
-  </si>
-  <si>
-    <t>28.00</t>
-  </si>
-  <si>
-    <t>29.40</t>
-  </si>
-  <si>
-    <t>VSAT_A00_8</t>
-  </si>
-  <si>
-    <t>29.50</t>
-  </si>
-  <si>
-    <t>VSAT_A00_9</t>
-  </si>
-  <si>
-    <t>VSAT_A01_1</t>
-  </si>
-  <si>
-    <t>VSAT_A01_2</t>
-  </si>
-  <si>
-    <t>VSAT_A01_3</t>
-  </si>
-  <si>
-    <t>VSAT_A01_4</t>
-  </si>
-  <si>
-    <t>VSAT_A01_5</t>
-  </si>
-  <si>
-    <t>VSAT_A01_6</t>
-  </si>
-  <si>
-    <t>VSAT_A01_7</t>
-  </si>
-  <si>
-    <t>VSAT_A01_8</t>
-  </si>
-  <si>
-    <t>VSAT_A01_9</t>
-  </si>
-  <si>
-    <t>VSAT_B00_1</t>
-  </si>
-  <si>
-    <t>VSAT_B00_2</t>
-  </si>
-  <si>
-    <t>VSAT_B00_3</t>
+    <t>Toán</t>
+  </si>
+  <si>
+    <t>132.00</t>
+  </si>
+  <si>
+    <t>150.00</t>
+  </si>
+  <si>
+    <t>8.50</t>
+  </si>
+  <si>
+    <t>VSAT_TOAN_3</t>
+  </si>
+  <si>
+    <t>128.50</t>
+  </si>
+  <si>
+    <t>8.10</t>
+  </si>
+  <si>
+    <t>VSAT_TOAN_5</t>
+  </si>
+  <si>
+    <t>122.50</t>
+  </si>
+  <si>
+    <t>7.75</t>
+  </si>
+  <si>
+    <t>VSAT_TOAN_10</t>
+  </si>
+  <si>
+    <t>114.50</t>
+  </si>
+  <si>
+    <t>7.00</t>
+  </si>
+  <si>
+    <t>VSAT_TOAN_20</t>
+  </si>
+  <si>
+    <t>108.00</t>
+  </si>
+  <si>
+    <t>6.60</t>
+  </si>
+  <si>
+    <t>VSAT_TOAN_30</t>
+  </si>
+  <si>
+    <t>102.50</t>
+  </si>
+  <si>
+    <t>VSAT_TOAN_40</t>
+  </si>
+  <si>
+    <t>97.00</t>
+  </si>
+  <si>
+    <t>6.00</t>
+  </si>
+  <si>
+    <t>VSAT_TOAN_50</t>
+  </si>
+  <si>
+    <t>91.00</t>
+  </si>
+  <si>
+    <t>5.60</t>
+  </si>
+  <si>
+    <t>VSAT_TOAN_60</t>
+  </si>
+  <si>
+    <t>85.00</t>
+  </si>
+  <si>
+    <t>5.25</t>
+  </si>
+  <si>
+    <t>VSAT_TOAN_70</t>
+  </si>
+  <si>
+    <t>77.00</t>
+  </si>
+  <si>
+    <t>5.00</t>
+  </si>
+  <si>
+    <t>VSAT_TOAN_80</t>
+  </si>
+  <si>
+    <t>68.00</t>
+  </si>
+  <si>
+    <t>4.50</t>
+  </si>
+  <si>
+    <t>VSAT_TOAN_90</t>
+  </si>
+  <si>
+    <t>1.50</t>
+  </si>
+  <si>
+    <t>VSAT_TOAN_90+</t>
+  </si>
+  <si>
+    <t>&gt;90%</t>
+  </si>
+  <si>
+    <t>Vật lí</t>
+  </si>
+  <si>
+    <t>123.00</t>
+  </si>
+  <si>
+    <t>147.00</t>
+  </si>
+  <si>
+    <t>9.50</t>
+  </si>
+  <si>
+    <t>VSAT_VATLI_3</t>
+  </si>
+  <si>
+    <t>118.50</t>
+  </si>
+  <si>
+    <t>9.25</t>
+  </si>
+  <si>
+    <t>VSAT_VATLI_5</t>
+  </si>
+  <si>
+    <t>112.50</t>
+  </si>
+  <si>
+    <t>9.00</t>
+  </si>
+  <si>
+    <t>VSAT_VATLI_10</t>
+  </si>
+  <si>
+    <t>105.00</t>
+  </si>
+  <si>
+    <t>VSAT_VATLI_20</t>
+  </si>
+  <si>
+    <t>99.50</t>
+  </si>
+  <si>
+    <t>8.00</t>
+  </si>
+  <si>
+    <t>VSAT_VATLI_30</t>
+  </si>
+  <si>
+    <t>94.50</t>
+  </si>
+  <si>
+    <t>VSAT_VATLI_40</t>
+  </si>
+  <si>
+    <t>90.00</t>
+  </si>
+  <si>
+    <t>VSAT_VATLI_50</t>
+  </si>
+  <si>
+    <t>7.25</t>
+  </si>
+  <si>
+    <t>VSAT_VATLI_60</t>
+  </si>
+  <si>
+    <t>80.00</t>
+  </si>
+  <si>
+    <t>6.75</t>
+  </si>
+  <si>
+    <t>VSAT_VATLI_70</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>VSAT_B00_4</t>
-  </si>
-  <si>
-    <t>VSAT_B00_5</t>
-  </si>
-  <si>
-    <t>VSAT_B00_6</t>
-  </si>
-  <si>
-    <t>VSAT_B00_7</t>
-  </si>
-  <si>
-    <t>VSAT_B00_8</t>
-  </si>
-  <si>
-    <t>VSAT_B00_9</t>
-  </si>
-  <si>
-    <t>VSAT_D01_1</t>
-  </si>
-  <si>
-    <t>VSAT_D01_2</t>
-  </si>
-  <si>
-    <t>VSAT_D01_3</t>
-  </si>
-  <si>
-    <t>VSAT_D01_4</t>
-  </si>
-  <si>
-    <t>VSAT_D01_5</t>
-  </si>
-  <si>
-    <t>VSAT_D01_6</t>
-  </si>
-  <si>
-    <t>VSAT_D01_7</t>
-  </si>
-  <si>
-    <t>VSAT_D01_8</t>
-  </si>
-  <si>
-    <t>VSAT_D01_9</t>
+    <t>74.00</t>
+  </si>
+  <si>
+    <t>6.35</t>
+  </si>
+  <si>
+    <t>VSAT_VATLI_80</t>
+  </si>
+  <si>
+    <t>66.50</t>
+  </si>
+  <si>
+    <t>5.75</t>
+  </si>
+  <si>
+    <t>VSAT_VATLI_90</t>
+  </si>
+  <si>
+    <t>17.00</t>
+  </si>
+  <si>
+    <t>3.05</t>
+  </si>
+  <si>
+    <t>VSAT_VATLI_90+</t>
+  </si>
+  <si>
+    <t>Hóa học</t>
+  </si>
+  <si>
+    <t>129.00</t>
+  </si>
+  <si>
+    <t>VSAT_HOAHOC_3</t>
+  </si>
+  <si>
+    <t>124.50</t>
+  </si>
+  <si>
+    <t>VSAT_HOAHOC_5</t>
+  </si>
+  <si>
+    <t>117.00</t>
+  </si>
+  <si>
+    <t>VSAT_HOAHOC_10</t>
+  </si>
+  <si>
+    <t>107.50</t>
+  </si>
+  <si>
+    <t>8.25</t>
+  </si>
+  <si>
+    <t>VSAT_HOAHOC_20</t>
+  </si>
+  <si>
+    <t>100.50</t>
+  </si>
+  <si>
+    <t>VSAT_HOAHOC_30</t>
+  </si>
+  <si>
+    <t>94.00</t>
+  </si>
+  <si>
+    <t>VSAT_HOAHOC_40</t>
+  </si>
+  <si>
+    <t>88.00</t>
+  </si>
+  <si>
+    <t>VSAT_HOAHOC_50</t>
+  </si>
+  <si>
+    <t>81.50</t>
+  </si>
+  <si>
+    <t>VSAT_HOAHOC_60</t>
+  </si>
+  <si>
+    <t>75.50</t>
+  </si>
+  <si>
+    <t>VSAT_HOAHOC_70</t>
+  </si>
+  <si>
+    <t>68.50</t>
+  </si>
+  <si>
+    <t>VSAT_HOAHOC_80</t>
+  </si>
+  <si>
+    <t>59.50</t>
+  </si>
+  <si>
+    <t>4.60</t>
+  </si>
+  <si>
+    <t>VSAT_HOAHOC_90</t>
+  </si>
+  <si>
+    <t>1.35</t>
+  </si>
+  <si>
+    <t>VSAT_HOAHOC_90+</t>
+  </si>
+  <si>
+    <t>Sinh học</t>
+  </si>
+  <si>
+    <t>130.50</t>
+  </si>
+  <si>
+    <t>9.75</t>
+  </si>
+  <si>
+    <t>VSAT_SINHHOC_3</t>
+  </si>
+  <si>
+    <t>126.50</t>
+  </si>
+  <si>
+    <t>VSAT_SINHHOC_5</t>
+  </si>
+  <si>
+    <t>120.50</t>
+  </si>
+  <si>
+    <t>8.34</t>
+  </si>
+  <si>
+    <t>VSAT_SINHHOC_10</t>
+  </si>
+  <si>
+    <t>7.85</t>
+  </si>
+  <si>
+    <t>VSAT_SINHHOC_20</t>
+  </si>
+  <si>
+    <t>105.50</t>
+  </si>
+  <si>
+    <t>VSAT_SINHHOC_30</t>
+  </si>
+  <si>
+    <t>100.00</t>
+  </si>
+  <si>
+    <t>VSAT_SINHHOC_40</t>
+  </si>
+  <si>
+    <t>6.85</t>
+  </si>
+  <si>
+    <t>VSAT_SINHHOC_50</t>
+  </si>
+  <si>
+    <t>88.50</t>
+  </si>
+  <si>
+    <t>6.50</t>
+  </si>
+  <si>
+    <t>VSAT_SINHHOC_60</t>
+  </si>
+  <si>
+    <t>82.50</t>
+  </si>
+  <si>
+    <t>VSAT_SINHHOC_70</t>
+  </si>
+  <si>
+    <t>76.00</t>
+  </si>
+  <si>
+    <t>5.85</t>
+  </si>
+  <si>
+    <t>VSAT_SINHHOC_80</t>
+  </si>
+  <si>
+    <t>VSAT_SINHHOC_90</t>
+  </si>
+  <si>
+    <t>26.50</t>
+  </si>
+  <si>
+    <t>2.80</t>
+  </si>
+  <si>
+    <t>VSAT_SINHHOC_90+</t>
+  </si>
+  <si>
+    <t>Lịch sử</t>
+  </si>
+  <si>
+    <t>133.50</t>
+  </si>
+  <si>
+    <t>VSAT_LICHSU_3</t>
+  </si>
+  <si>
+    <t>131.00</t>
+  </si>
+  <si>
+    <t>VSAT_LICHSU_5</t>
+  </si>
+  <si>
+    <t>VSAT_LICHSU_10</t>
+  </si>
+  <si>
+    <t>VSAT_LICHSU_20</t>
+  </si>
+  <si>
+    <t>115.00</t>
+  </si>
+  <si>
+    <t>VSAT_LICHSU_30</t>
+  </si>
+  <si>
+    <t>110.00</t>
+  </si>
+  <si>
+    <t>VSAT_LICHSU_40</t>
+  </si>
+  <si>
+    <t>VSAT_LICHSU_50</t>
+  </si>
+  <si>
+    <t>101.00</t>
+  </si>
+  <si>
+    <t>VSAT_LICHSU_60</t>
+  </si>
+  <si>
+    <t>95.50</t>
+  </si>
+  <si>
+    <t>VSAT_LICHSU_70</t>
+  </si>
+  <si>
+    <t>VSAT_LICHSU_80</t>
+  </si>
+  <si>
+    <t>79.50</t>
+  </si>
+  <si>
+    <t>VSAT_LICHSU_90</t>
+  </si>
+  <si>
+    <t>36.50</t>
+  </si>
+  <si>
+    <t>2.95</t>
+  </si>
+  <si>
+    <t>VSAT_LICHSU_90+</t>
+  </si>
+  <si>
+    <t>Địa lí</t>
+  </si>
+  <si>
+    <t>124.00</t>
+  </si>
+  <si>
+    <t>141.00</t>
+  </si>
+  <si>
+    <t>VSAT_DIALI_3</t>
+  </si>
+  <si>
+    <t>VSAT_DIALI_5</t>
+  </si>
+  <si>
+    <t>115.50</t>
+  </si>
+  <si>
+    <t>VSAT_DIALI_10</t>
+  </si>
+  <si>
+    <t>108.50</t>
+  </si>
+  <si>
+    <t>VSAT_DIALI_20</t>
+  </si>
+  <si>
+    <t>103.00</t>
+  </si>
+  <si>
+    <t>VSAT_DIALI_30</t>
+  </si>
+  <si>
+    <t>98.50</t>
+  </si>
+  <si>
+    <t>VSAT_DIALI_40</t>
+  </si>
+  <si>
+    <t>VSAT_DIALI_50</t>
+  </si>
+  <si>
+    <t>89.50</t>
+  </si>
+  <si>
+    <t>VSAT_DIALI_60</t>
+  </si>
+  <si>
+    <t>84.50</t>
+  </si>
+  <si>
+    <t>VSAT_DIALI_70</t>
+  </si>
+  <si>
+    <t>79.00</t>
+  </si>
+  <si>
+    <t>VSAT_DIALI_80</t>
+  </si>
+  <si>
+    <t>71.00</t>
+  </si>
+  <si>
+    <t>VSAT_DIALI_90</t>
+  </si>
+  <si>
+    <t>31.00</t>
+  </si>
+  <si>
+    <t>3.00</t>
+  </si>
+  <si>
+    <t>VSAT_DIALI_90+</t>
+  </si>
+  <si>
+    <t>Tiếng Anh</t>
+  </si>
+  <si>
+    <t>VSAT_TIENGANH_3</t>
+  </si>
+  <si>
+    <t>127.50</t>
+  </si>
+  <si>
+    <t>VSAT_TIENGANH_5</t>
+  </si>
+  <si>
+    <t>VSAT_TIENGANH_10</t>
+  </si>
+  <si>
+    <t>112.00</t>
+  </si>
+  <si>
+    <t>VSAT_TIENGANH_20</t>
+  </si>
+  <si>
+    <t>VSAT_TIENGANH_30</t>
+  </si>
+  <si>
+    <t>VSAT_TIENGANH_40</t>
+  </si>
+  <si>
+    <t>92.00</t>
+  </si>
+  <si>
+    <t>5.50</t>
+  </si>
+  <si>
+    <t>VSAT_TIENGANH_50</t>
+  </si>
+  <si>
+    <t>85.50</t>
+  </si>
+  <si>
+    <t>VSAT_TIENGANH_60</t>
+  </si>
+  <si>
+    <t>78.50</t>
+  </si>
+  <si>
+    <t>VSAT_TIENGANH_70</t>
+  </si>
+  <si>
+    <t>70.50</t>
+  </si>
+  <si>
+    <t>VSAT_TIENGANH_80</t>
+  </si>
+  <si>
+    <t>60.00</t>
+  </si>
+  <si>
+    <t>4.00</t>
+  </si>
+  <si>
+    <t>VSAT_TIENGANH_90</t>
+  </si>
+  <si>
+    <t>20.50</t>
+  </si>
+  <si>
+    <t>1.25</t>
+  </si>
+  <si>
+    <t>VSAT_TIENGANH_90+</t>
+  </si>
+  <si>
+    <t>Ngữ văn</t>
+  </si>
+  <si>
+    <t>129.50</t>
+  </si>
+  <si>
+    <t>146.00</t>
+  </si>
+  <si>
+    <t>VSAT_NGU VAN_3</t>
+  </si>
+  <si>
+    <t>VSAT_NGU VAN_5</t>
+  </si>
+  <si>
+    <t>VSAT_NGU VAN_10</t>
+  </si>
+  <si>
+    <t>119.50</t>
+  </si>
+  <si>
+    <t>VSAT_NGU VAN_20</t>
+  </si>
+  <si>
+    <t>VSAT_NGU VAN_30</t>
+  </si>
+  <si>
+    <t>VSAT_NGU VAN_40</t>
+  </si>
+  <si>
+    <t>109.00</t>
+  </si>
+  <si>
+    <t>VSAT_NGU VAN_50</t>
+  </si>
+  <si>
+    <t>106.00</t>
+  </si>
+  <si>
+    <t>VSAT_NGU VAN_60</t>
+  </si>
+  <si>
+    <t>102.00</t>
+  </si>
+  <si>
+    <t>VSAT_NGU VAN_70</t>
+  </si>
+  <si>
+    <t>VSAT_NGU VAN_80</t>
+  </si>
+  <si>
+    <t>VSAT_NGU VAN_90</t>
+  </si>
+  <si>
+    <t>3.50</t>
+  </si>
+  <si>
+    <t>VSAT_NGU VAN_90+</t>
   </si>
   <si>
     <t>NGOAINGU</t>
@@ -702,7 +1203,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -711,21 +1212,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1" tint="0.149998474074526"/>
+      <sz val="10"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1" tint="0.149998474074526"/>
+      <sz val="10"/>
       <name val="Calibri"/>
       <charset val="163"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1" tint="0.149998474074526"/>
+      <name val="Segoe UI"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -881,12 +1384,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1205,31 +1714,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1238,37 +1744,37 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1283,82 +1789,94 @@
     <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1683,7 +2201,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P125"/>
+  <dimension ref="A1:P185"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="18.6666666666667" customWidth="1"/>
@@ -1692,7 +2210,7 @@
     <col min="9" max="9" width="26.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" ht="15" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1724,7 +2242,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" ht="15" spans="1:10">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1754,7 +2272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" ht="15" spans="1:10">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1784,7 +2302,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" ht="15" spans="1:10">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1814,7 +2332,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" ht="15" spans="1:10">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1844,7 +2362,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" ht="15" spans="1:10">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1874,7 +2392,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" ht="15" spans="1:10">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1904,7 +2422,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" ht="15" spans="1:10">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1934,7 +2452,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" ht="15" spans="1:10">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1964,7 +2482,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" ht="15" spans="1:10">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1994,7 +2512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" ht="15" spans="1:10">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -2024,7 +2542,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" ht="15" spans="1:10">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -2054,7 +2572,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" ht="15" spans="1:10">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2084,7 +2602,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" ht="15" spans="1:10">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -2114,7 +2632,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" ht="15" spans="1:10">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2144,7 +2662,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" ht="15" spans="1:10">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -2174,7 +2692,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" ht="15" spans="1:10">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -2204,7 +2722,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" ht="15" spans="1:10">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -2234,7 +2752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" ht="15" spans="1:10">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -2264,7 +2782,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" ht="15" spans="1:10">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -2294,7 +2812,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" ht="15" spans="1:10">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -2324,7 +2842,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" ht="15" spans="1:10">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -2354,7 +2872,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" ht="15" spans="1:10">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -2384,7 +2902,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" ht="15" spans="1:10">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -2414,7 +2932,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" ht="15" spans="1:10">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -2444,7 +2962,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" ht="15" spans="1:10">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -2474,7 +2992,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" ht="15" spans="1:10">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -2504,7 +3022,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" ht="15" spans="1:10">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -2534,7 +3052,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" ht="15" spans="1:10">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -2564,7 +3082,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" ht="15" spans="1:10">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -2594,7 +3112,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" ht="15" spans="1:10">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -2624,7 +3142,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" ht="15" spans="1:10">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -2654,7 +3172,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" ht="15" spans="1:10">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -2684,7 +3202,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" ht="15" spans="1:10">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -2714,7 +3232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" ht="15" spans="1:10">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -2744,7 +3262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" ht="15" spans="1:10">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -2774,7 +3292,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" ht="15" spans="1:10">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -2804,7 +3322,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" ht="15" spans="1:10">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -2834,7 +3352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" ht="15" spans="1:10">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -2864,7 +3382,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" ht="15" spans="1:10">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -2894,7 +3412,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" ht="15" spans="1:10">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -2924,7 +3442,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" ht="15" spans="1:10">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -2954,7 +3472,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" ht="15" spans="1:10">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -2984,7 +3502,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" ht="15" spans="1:10">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -3014,7 +3532,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" ht="15" spans="1:10">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -3044,7 +3562,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" ht="15" spans="1:10">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -3074,7 +3592,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" ht="15" spans="1:10">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -3104,7 +3622,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" ht="15" spans="1:10">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -3134,7 +3652,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" ht="15" spans="1:10">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -3164,7 +3682,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" ht="15" spans="1:10">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -3194,7 +3712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" ht="15" spans="1:10">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -3224,7 +3742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" ht="15" spans="1:10">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -3254,7 +3772,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" ht="15" spans="1:10">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -3284,7 +3802,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" ht="15" spans="1:10">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -3314,7 +3832,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" ht="15" spans="1:10">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -3344,7 +3862,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" ht="15" spans="1:10">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -3374,7 +3892,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" ht="15" spans="1:10">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -3404,7 +3922,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" ht="15" spans="1:10">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -3434,7 +3952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" ht="15" spans="1:10">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -3464,7 +3982,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" ht="15" spans="1:10">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -3494,7 +4012,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" ht="15" spans="1:10">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -3524,7 +4042,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" ht="15" spans="1:10">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -3554,7 +4072,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" ht="15" spans="1:10">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -3584,7 +4102,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" ht="15" spans="1:10">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -3614,7 +4132,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" ht="15" spans="1:10">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -3644,1807 +4162,3627 @@
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" ht="15" spans="1:10">
       <c r="A66" s="1">
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1">
-        <v>100</v>
-      </c>
-      <c r="F66" s="1">
-        <v>149</v>
-      </c>
-      <c r="G66" s="1" t="s">
+      <c r="C66" s="2"/>
+      <c r="D66" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="H66" s="1" t="s">
+      <c r="E66" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="I66" s="1" t="s">
+      <c r="F66" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="J66" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10">
+      <c r="G66" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J66" s="4">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="67" ht="15" spans="1:10">
       <c r="A67" s="1">
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D67" s="1"/>
-      <c r="E67" s="1">
-        <v>150</v>
-      </c>
-      <c r="F67" s="1">
-        <v>199</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H67" s="1" t="s">
+      <c r="C67" s="2"/>
+      <c r="D67" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H67" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="I67" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="J67" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10">
+      <c r="I67" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J67" s="4">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="68" ht="15" spans="1:10">
       <c r="A68" s="1">
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1">
-        <v>200</v>
-      </c>
-      <c r="F68" s="1">
-        <v>249</v>
-      </c>
-      <c r="G68" s="1" t="s">
+      <c r="C68" s="2"/>
+      <c r="D68" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F68" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H68" s="1" t="s">
+      <c r="G68" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H68" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I68" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="J68" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10">
+      <c r="I68" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J68" s="4">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="69" ht="15" spans="1:10">
       <c r="A69" s="1">
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1">
-        <v>250</v>
-      </c>
-      <c r="F69" s="1">
-        <v>299</v>
-      </c>
-      <c r="G69" s="1" t="s">
+      <c r="C69" s="2"/>
+      <c r="D69" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F69" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H69" s="1" t="s">
+      <c r="G69" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H69" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="I69" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="J69" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10">
+      <c r="I69" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J69" s="4">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="70" ht="15" spans="1:10">
       <c r="A70" s="1">
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1">
-        <v>300</v>
-      </c>
-      <c r="F70" s="1">
-        <v>349</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H70" s="1" t="s">
+      <c r="C70" s="2"/>
+      <c r="D70" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F70" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="I70" s="1" t="s">
+      <c r="G70" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H70" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="J70" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10">
+      <c r="I70" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J70" s="4">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="71" ht="15" spans="1:10">
       <c r="A71" s="1">
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1">
-        <v>350</v>
-      </c>
-      <c r="F71" s="1">
-        <v>399</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="H71" s="1" t="s">
+      <c r="C71" s="2"/>
+      <c r="D71" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F71" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="I71" s="1" t="s">
+      <c r="G71" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H71" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="J71" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10">
+      <c r="I71" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J71" s="4">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="72" ht="15" spans="1:10">
       <c r="A72" s="1">
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1">
-        <v>400</v>
-      </c>
-      <c r="F72" s="1">
-        <v>419</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="H72" s="1" t="s">
+      <c r="C72" s="2"/>
+      <c r="D72" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F72" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="I72" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="J72" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10">
+      <c r="G72" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J72" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="73" ht="15" spans="1:10">
       <c r="A73" s="1">
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1">
-        <v>420</v>
-      </c>
-      <c r="F73" s="1">
-        <v>439</v>
-      </c>
-      <c r="G73" s="1" t="s">
+      <c r="C73" s="2"/>
+      <c r="D73" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F73" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="G73" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H73" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="I73" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J73" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10">
+      <c r="I73" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="J73" s="4">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="74" ht="15" spans="1:10">
       <c r="A74" s="1">
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1">
-        <v>440</v>
-      </c>
-      <c r="F74" s="1">
-        <v>450</v>
-      </c>
-      <c r="G74" s="1" t="s">
+      <c r="C74" s="2"/>
+      <c r="D74" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F74" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="H74" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I74" s="1" t="s">
+      <c r="G74" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H74" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="J74" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10">
+      <c r="I74" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="J74" s="4">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="75" ht="15" spans="1:10">
       <c r="A75" s="1">
         <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1">
-        <v>100</v>
-      </c>
-      <c r="F75" s="1">
+      <c r="C75" s="2"/>
+      <c r="D75" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E75" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G75" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="J75" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10">
+      <c r="F75" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="J75" s="4">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="76" ht="15" spans="1:10">
       <c r="A76" s="1">
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D76" s="1"/>
-      <c r="E76" s="1">
+      <c r="C76" s="2"/>
+      <c r="D76" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H76" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F76" s="1">
-        <v>199</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J76" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10">
+      <c r="I76" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="J76" s="4">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="77" ht="15" spans="1:10">
       <c r="A77" s="1">
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D77" s="1"/>
-      <c r="E77" s="1">
-        <v>200</v>
-      </c>
-      <c r="F77" s="1">
-        <v>249</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="H77" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="I77" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="J77" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10">
+      <c r="C77" s="2"/>
+      <c r="D77" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="78" ht="15" spans="1:10">
       <c r="A78" s="1">
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1">
-        <v>250</v>
-      </c>
-      <c r="F78" s="1">
-        <v>299</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="I78" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J78" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10">
+      <c r="C78" s="2"/>
+      <c r="D78" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="J78" s="4">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="79" ht="15" spans="1:10">
       <c r="A79" s="1">
         <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1">
-        <v>300</v>
-      </c>
-      <c r="F79" s="1">
-        <v>349</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="J79" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10">
+      <c r="C79" s="2"/>
+      <c r="D79" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="J79" s="4">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="80" ht="15" spans="1:10">
       <c r="A80" s="1">
         <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C80" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D80" s="1"/>
-      <c r="E80" s="1">
-        <v>350</v>
-      </c>
-      <c r="F80" s="1">
-        <v>399</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J80" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10">
+      <c r="C80" s="2"/>
+      <c r="D80" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J80" s="4">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="81" ht="15" spans="1:10">
       <c r="A81" s="1">
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C81" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D81" s="1"/>
-      <c r="E81" s="1">
-        <v>400</v>
-      </c>
-      <c r="F81" s="1">
-        <v>419</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="J81" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10">
+      <c r="C81" s="2"/>
+      <c r="D81" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J81" s="4">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="82" ht="15" spans="1:10">
       <c r="A82" s="1">
         <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C82" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1">
-        <v>420</v>
-      </c>
-      <c r="F82" s="1">
-        <v>439</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="J82" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10">
+      <c r="C82" s="2"/>
+      <c r="D82" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="J82" s="4">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="83" ht="15" spans="1:10">
       <c r="A83" s="1">
         <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1">
-        <v>440</v>
-      </c>
-      <c r="F83" s="1">
-        <v>450</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="J83" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10">
+      <c r="C83" s="2"/>
+      <c r="D83" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J83" s="4">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="84" ht="15" spans="1:10">
       <c r="A84" s="1">
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D84" s="1"/>
-      <c r="E84" s="1">
-        <v>100</v>
-      </c>
-      <c r="F84" s="1">
-        <v>149</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="J84" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10">
+      <c r="C84" s="2"/>
+      <c r="D84" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J84" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="85" ht="15" spans="1:10">
       <c r="A85" s="1">
         <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C85" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D85" s="1"/>
-      <c r="E85" s="1">
-        <v>150</v>
-      </c>
-      <c r="F85" s="1">
-        <v>199</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J85" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16">
+      <c r="C85" s="2"/>
+      <c r="D85" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J85" s="4">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="86" ht="15" spans="1:16">
       <c r="A86" s="1">
         <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D86" s="1"/>
-      <c r="E86" s="1">
-        <v>200</v>
-      </c>
-      <c r="F86" s="1">
-        <v>249</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J86" s="1">
-        <v>3</v>
+      <c r="C86" s="2"/>
+      <c r="D86" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="J86" s="4">
+        <v>0.7</v>
       </c>
       <c r="P86" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="87" ht="15" spans="1:10">
       <c r="A87" s="1">
         <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D87" s="1"/>
-      <c r="E87" s="1">
-        <v>250</v>
-      </c>
-      <c r="F87" s="1">
-        <v>299</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="I87" s="1" t="s">
+      <c r="C87" s="2"/>
+      <c r="D87" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="J87" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10">
+      <c r="E87" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="J87" s="4">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="88" ht="15" spans="1:10">
       <c r="A88" s="1">
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D88" s="1"/>
-      <c r="E88" s="1">
-        <v>300</v>
-      </c>
-      <c r="F88" s="1">
-        <v>349</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H88" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="I88" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="J88" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10">
+      <c r="C88" s="2"/>
+      <c r="D88" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J88" s="4">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="89" ht="15" spans="1:10">
       <c r="A89" s="1">
         <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D89" s="1"/>
-      <c r="E89" s="1">
-        <v>350</v>
-      </c>
-      <c r="F89" s="1">
-        <v>399</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I89" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="J89" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10">
+      <c r="C89" s="2"/>
+      <c r="D89" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="90" ht="15" spans="1:10">
       <c r="A90" s="1">
         <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C90" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1">
-        <v>400</v>
-      </c>
-      <c r="F90" s="1">
-        <v>419</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I90" s="1" t="s">
+      <c r="C90" s="2"/>
+      <c r="D90" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G90" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="J90" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10">
+      <c r="H90" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="J90" s="4">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="91" ht="15" spans="1:10">
       <c r="A91" s="1">
         <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D91" s="1"/>
-      <c r="E91" s="1">
-        <v>420</v>
-      </c>
-      <c r="F91" s="1">
-        <v>439</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="J91" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10">
+      <c r="C91" s="2"/>
+      <c r="D91" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="J91" s="4">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="92" ht="15" spans="1:10">
       <c r="A92" s="1">
         <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1">
-        <v>440</v>
-      </c>
-      <c r="F92" s="1">
-        <v>450</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="J92" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10">
+      <c r="C92" s="2"/>
+      <c r="D92" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="J92" s="4">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="93" ht="15" spans="1:10">
       <c r="A93" s="1">
         <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D93" s="1"/>
-      <c r="E93" s="1">
-        <v>100</v>
-      </c>
-      <c r="F93" s="1">
-        <v>149</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="J93" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10">
+      <c r="C93" s="2"/>
+      <c r="D93" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="J93" s="4">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="94" ht="15" spans="1:10">
       <c r="A94" s="1">
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1">
-        <v>150</v>
-      </c>
-      <c r="F94" s="1">
-        <v>199</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="J94" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10">
+      <c r="C94" s="2"/>
+      <c r="D94" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="J94" s="4">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="95" ht="15" spans="1:10">
       <c r="A95" s="1">
         <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1">
-        <v>200</v>
-      </c>
-      <c r="F95" s="1">
-        <v>249</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="I95" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="J95" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10">
+      <c r="C95" s="2"/>
+      <c r="D95" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J95" s="4">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="96" ht="15" spans="1:10">
       <c r="A96" s="1">
         <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D96" s="1"/>
-      <c r="E96" s="1">
-        <v>250</v>
-      </c>
-      <c r="F96" s="1">
-        <v>299</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="H96" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="I96" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="J96" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10">
+      <c r="C96" s="2"/>
+      <c r="D96" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J96" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="97" ht="15" spans="1:10">
       <c r="A97" s="1">
         <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D97" s="1"/>
-      <c r="E97" s="1">
-        <v>300</v>
-      </c>
-      <c r="F97" s="1">
-        <v>349</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="J97" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10">
+      <c r="C97" s="2"/>
+      <c r="D97" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="J97" s="4">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="98" ht="15" spans="1:10">
       <c r="A98" s="1">
         <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D98" s="1"/>
-      <c r="E98" s="1">
-        <v>350</v>
-      </c>
-      <c r="F98" s="1">
-        <v>399</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="J98" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14">
+      <c r="C98" s="2"/>
+      <c r="D98" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J98" s="4">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="99" ht="15" spans="1:10">
       <c r="A99" s="1">
         <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D99" s="1"/>
-      <c r="E99" s="1">
-        <v>400</v>
-      </c>
-      <c r="F99" s="1">
-        <v>419</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J99" s="1">
-        <v>7</v>
-      </c>
-      <c r="N99" s="4"/>
-    </row>
-    <row r="100" spans="1:10">
+      <c r="C99" s="2"/>
+      <c r="D99" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="J99" s="4">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="100" ht="15" spans="1:10">
       <c r="A100" s="1">
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D100" s="1"/>
-      <c r="E100" s="1">
-        <v>420</v>
-      </c>
-      <c r="F100" s="1">
-        <v>439</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="J100" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10">
+      <c r="C100" s="2"/>
+      <c r="D100" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="J100" s="4">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="101" ht="15" spans="1:10">
       <c r="A101" s="1">
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D101" s="1"/>
-      <c r="E101" s="1">
-        <v>440</v>
-      </c>
-      <c r="F101" s="1">
-        <v>450</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="J101" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10">
+      <c r="C101" s="2"/>
+      <c r="D101" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="102" ht="15" spans="1:10">
       <c r="A102" s="1">
         <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" s="3" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>175</v>
+        <v>221</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>176</v>
+        <v>123</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>177</v>
+        <v>222</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="J102" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10">
+        <v>223</v>
+      </c>
+      <c r="J102" s="4">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="103" ht="15" spans="1:10">
       <c r="A103" s="1">
         <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="3" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>179</v>
+        <v>224</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>180</v>
+        <v>221</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="J103" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10">
+        <v>225</v>
+      </c>
+      <c r="J103" s="4">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="104" ht="15" spans="1:10">
       <c r="A104" s="1">
         <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" s="3" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>183</v>
+        <v>226</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>184</v>
+        <v>224</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>184</v>
+        <v>227</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>184</v>
+        <v>18</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="J104" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10">
+        <v>228</v>
+      </c>
+      <c r="J104" s="4">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="105" ht="15" spans="1:10">
       <c r="A105" s="1">
         <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E105" s="3">
-        <v>450</v>
-      </c>
-      <c r="F105" s="3">
-        <v>499</v>
+        <v>220</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>226</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>177</v>
+        <v>229</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>177</v>
+        <v>227</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J105" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10">
+        <v>230</v>
+      </c>
+      <c r="J105" s="4">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="106" ht="15" spans="1:10">
       <c r="A106" s="1">
         <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E106" s="3">
-        <v>500</v>
-      </c>
-      <c r="F106" s="3">
-        <v>626</v>
+        <v>220</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>166</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>181</v>
+        <v>15</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="J106" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10">
+        <v>232</v>
+      </c>
+      <c r="J106" s="4">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="107" ht="15" spans="1:10">
       <c r="A107" s="1">
         <v>106</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E107" s="3">
-        <v>627</v>
-      </c>
-      <c r="F107" s="3">
-        <v>990</v>
+        <v>220</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>231</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>184</v>
+        <v>15</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="J107" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10">
+        <v>234</v>
+      </c>
+      <c r="J107" s="4">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="108" ht="15" spans="1:10">
       <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="J108" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="109" ht="15" spans="1:10">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="J109" s="4">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="110" ht="15" spans="1:10">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="J110" s="4">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="111" ht="15" spans="1:10">
+      <c r="A111" s="1">
         <v>110</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C108" s="1"/>
-      <c r="D108" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E108" s="1">
-        <v>450</v>
-      </c>
-      <c r="F108" s="1">
-        <v>499</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="H108" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="I108" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="J108" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10">
-      <c r="A109" s="1">
+      <c r="B111" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="J111" s="4">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="112" ht="15" spans="1:10">
+      <c r="A112" s="1">
         <v>111</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C109" s="1"/>
-      <c r="D109" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E109" s="1">
-        <v>500</v>
-      </c>
-      <c r="F109" s="1">
-        <v>626</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J109" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10">
-      <c r="A110" s="1">
+      <c r="B112" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="J112" s="4">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="113" ht="15" spans="1:10">
+      <c r="A113" s="1">
         <v>112</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C110" s="1"/>
-      <c r="D110" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E110" s="1">
-        <v>627</v>
-      </c>
-      <c r="F110" s="1">
-        <v>677</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="I110" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="J110" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10">
-      <c r="A111" s="1">
+      <c r="B113" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="J113" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="114" ht="15" spans="1:10">
+      <c r="A114" s="1">
         <v>113</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C111" s="1"/>
-      <c r="D111" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="E111" s="1">
-        <v>30</v>
-      </c>
-      <c r="F111" s="1">
-        <v>45</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="I111" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="J111" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10">
-      <c r="A112" s="1">
-        <v>114</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C112" s="1"/>
-      <c r="D112" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="E112" s="1">
-        <v>46</v>
-      </c>
-      <c r="F112" s="1">
-        <v>93</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="H112" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="I112" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="J112" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10">
-      <c r="A113" s="1">
-        <v>115</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C113" s="1"/>
-      <c r="D113" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="E113" s="1">
-        <v>94</v>
-      </c>
-      <c r="F113" s="1">
-        <v>120</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="I113" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="J113" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10">
-      <c r="A114" s="1">
-        <v>107</v>
-      </c>
       <c r="B114" s="1" t="s">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="3" t="s">
-        <v>198</v>
+        <v>249</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>199</v>
+        <v>250</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>199</v>
+        <v>123</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>177</v>
+        <v>222</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>177</v>
+        <v>21</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="J114" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10">
+        <v>251</v>
+      </c>
+      <c r="J114" s="4">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="115" ht="15" spans="1:10">
       <c r="A115" s="1">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="3" t="s">
-        <v>198</v>
+        <v>249</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>201</v>
+        <v>252</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>201</v>
+        <v>250</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="J115" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10">
+        <v>253</v>
+      </c>
+      <c r="J115" s="4">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="116" ht="15" spans="1:10">
       <c r="A116" s="1">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="3" t="s">
-        <v>198</v>
+        <v>249</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>203</v>
+        <v>252</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="J116" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10">
+        <v>254</v>
+      </c>
+      <c r="J116" s="4">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="117" ht="15" spans="1:10">
       <c r="A117" s="1">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C117" s="1"/>
-      <c r="D117" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="E117" s="1">
-        <v>140</v>
-      </c>
-      <c r="F117" s="1">
-        <v>159</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="H117" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="I117" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="J117" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10">
+        <v>120</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="J117" s="4">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="118" ht="15" spans="1:10">
       <c r="A118" s="1">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C118" s="1"/>
-      <c r="D118" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="E118" s="1">
-        <v>160</v>
-      </c>
-      <c r="F118" s="1">
-        <v>179</v>
-      </c>
-      <c r="G118" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="H118" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="I118" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="J118" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10">
+        <v>120</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="J118" s="4">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="119" ht="15" spans="1:10">
       <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="H119" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C119" s="1"/>
-      <c r="D119" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="E119" s="1">
-        <v>180</v>
-      </c>
-      <c r="F119" s="1">
-        <v>210</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H119" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="I119" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="J119" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10">
+      <c r="I119" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="J119" s="4">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="120" ht="15" spans="1:10">
       <c r="A120" s="1">
         <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C120" s="1"/>
-      <c r="D120" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="E120" s="1">
-        <v>43</v>
-      </c>
-      <c r="F120" s="1">
-        <v>58</v>
-      </c>
-      <c r="G120" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="H120" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="I120" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="J120" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10">
+        <v>120</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="J120" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="121" ht="15" spans="1:10">
       <c r="A121" s="1">
         <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C121" s="1"/>
-      <c r="D121" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="E121" s="1">
-        <v>59</v>
-      </c>
-      <c r="F121" s="1">
-        <v>75</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="H121" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="I121" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="J121" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10">
+        <v>120</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="J121" s="4">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="122" ht="15" spans="1:10">
       <c r="A122" s="1">
         <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="J122" s="4">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="123" ht="15" spans="1:10">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="J123" s="4">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="124" ht="15" spans="1:10">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="J124" s="4">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="125" ht="15" spans="1:10">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I125" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="J125" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="126" ht="15" spans="1:10">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="J126" s="4">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="127" ht="15" spans="1:10">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I127" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="J127" s="4">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="128" ht="15" spans="1:10">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="J128" s="4">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="129" ht="15" spans="1:10">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H129" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I129" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="J129" s="4">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="130" ht="15" spans="1:10">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H130" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I130" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="J130" s="4">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="131" ht="15" spans="1:10">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H131" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="I131" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="J131" s="4">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="132" ht="15" spans="1:10">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H132" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I132" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="J132" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="133" ht="15" spans="1:10">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I133" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J133" s="4">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="134" ht="15" spans="1:10">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="J134" s="4">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="135" ht="15" spans="1:10">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H135" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I135" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="J135" s="4">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="136" ht="15" spans="1:10">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="H136" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I136" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="J136" s="4">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="137" ht="15" spans="1:10">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="H137" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="I137" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="J137" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="138" ht="15" spans="1:10">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I138" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="J138" s="4">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="139" ht="15" spans="1:14">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H139" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I139" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="J139" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="N139" s="7"/>
+    </row>
+    <row r="140" ht="15" spans="1:14">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H140" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="J140" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="N140" s="7"/>
+    </row>
+    <row r="141" ht="15" spans="1:14">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="H141" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I141" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="J141" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="N141" s="7"/>
+    </row>
+    <row r="142" ht="15" spans="1:14">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H142" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="I142" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="J142" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="N142" s="7"/>
+    </row>
+    <row r="143" ht="15" spans="1:14">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C143" s="2"/>
+      <c r="D143" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H143" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="I143" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="J143" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="N143" s="7"/>
+    </row>
+    <row r="144" ht="15" spans="1:14">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="H144" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="I144" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="J144" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="N144" s="7"/>
+    </row>
+    <row r="145" ht="15" spans="1:14">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H145" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="I145" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="J145" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="N145" s="7"/>
+    </row>
+    <row r="146" ht="15" spans="1:14">
+      <c r="A146" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="H146" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="J146" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="N146" s="7"/>
+    </row>
+    <row r="147" ht="15" spans="1:14">
+      <c r="A147" s="1">
+        <v>146</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H147" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="I147" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="J147" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="N147" s="7"/>
+    </row>
+    <row r="148" ht="15" spans="1:14">
+      <c r="A148" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="D148" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="H148" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="I148" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="J148" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="N148" s="7"/>
+    </row>
+    <row r="149" ht="15" spans="1:14">
+      <c r="A149" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C149" s="2"/>
+      <c r="D149" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G149" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="H149" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="I149" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="J149" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="N149" s="7"/>
+    </row>
+    <row r="150" ht="15" spans="1:14">
+      <c r="A150" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C150" s="2"/>
+      <c r="D150" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H150" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I150" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="J150" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="N150" s="7"/>
+    </row>
+    <row r="151" ht="15" spans="1:14">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C151" s="2"/>
+      <c r="D151" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H151" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I151" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="J151" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="N151" s="7"/>
+    </row>
+    <row r="152" ht="15" spans="1:14">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="D152" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H152" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="I152" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="J152" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="N152" s="7"/>
+    </row>
+    <row r="153" ht="15" spans="1:14">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C153" s="2"/>
+      <c r="D153" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H153" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="I153" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="J153" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="N153" s="7"/>
+    </row>
+    <row r="154" ht="15" spans="1:14">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C154" s="2"/>
+      <c r="D154" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H154" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I154" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="J154" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="N154" s="7"/>
+    </row>
+    <row r="155" ht="15" spans="1:14">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C155" s="2"/>
+      <c r="D155" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="H155" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I155" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="J155" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="N155" s="7"/>
+    </row>
+    <row r="156" ht="15" spans="1:14">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C156" s="2"/>
+      <c r="D156" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H156" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="I156" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="J156" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="N156" s="7"/>
+    </row>
+    <row r="157" ht="15" spans="1:14">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C157" s="2"/>
+      <c r="D157" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H157" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I157" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="J157" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="N157" s="7"/>
+    </row>
+    <row r="158" ht="15" spans="1:14">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C158" s="2"/>
+      <c r="D158" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H158" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I158" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="J158" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="N158" s="7"/>
+    </row>
+    <row r="159" ht="15" spans="1:14">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C159" s="2"/>
+      <c r="D159" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H159" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I159" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="J159" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="N159" s="7"/>
+    </row>
+    <row r="160" ht="15" spans="1:10">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C160" s="2"/>
+      <c r="D160" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="H160" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I160" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="J160" s="4">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="161" ht="15" spans="1:10">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C161" s="2"/>
+      <c r="D161" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="H161" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I161" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="J161" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="162" ht="15" spans="1:10">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C162" s="5"/>
+      <c r="D162" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="E162" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="F162" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="G162" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="H162" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="I162" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="J162" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="163" ht="15" spans="1:10">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C163" s="5"/>
+      <c r="D163" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="F163" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="G163" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="H163" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="I163" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="J163" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" ht="15" spans="1:10">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C164" s="5"/>
+      <c r="D164" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="E164" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="F164" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="G164" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H164" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="I164" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="J164" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165" ht="15" spans="1:10">
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C165" s="5"/>
+      <c r="D165" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="E165" s="6">
+        <v>450</v>
+      </c>
+      <c r="F165" s="6">
+        <v>499</v>
+      </c>
+      <c r="G165" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="H165" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="I165" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="J165" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="166" ht="15" spans="1:10">
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C166" s="5"/>
+      <c r="D166" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="E166" s="6">
+        <v>500</v>
+      </c>
+      <c r="F166" s="6">
+        <v>626</v>
+      </c>
+      <c r="G166" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="H166" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="I166" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="J166" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" ht="15" spans="1:10">
+      <c r="A167" s="1">
+        <v>166</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C167" s="5"/>
+      <c r="D167" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="E167" s="6">
+        <v>627</v>
+      </c>
+      <c r="F167" s="6">
+        <v>990</v>
+      </c>
+      <c r="G167" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H167" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="I167" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="J167" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="168" ht="15" spans="1:10">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C168" s="1"/>
+      <c r="D168" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="E168" s="1">
+        <v>450</v>
+      </c>
+      <c r="F168" s="1">
+        <v>499</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="H168" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="I168" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="J168" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="169" ht="15" spans="1:10">
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C169" s="1"/>
+      <c r="D169" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="E169" s="1">
+        <v>500</v>
+      </c>
+      <c r="F169" s="1">
+        <v>626</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H169" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="I169" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="J169" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" ht="15" spans="1:10">
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C170" s="1"/>
+      <c r="D170" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="E170" s="1">
+        <v>627</v>
+      </c>
+      <c r="F170" s="1">
+        <v>677</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="H170" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="I170" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="J170" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="171" ht="15" spans="1:10">
+      <c r="A171" s="1">
+        <v>170</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C171" s="1"/>
+      <c r="D171" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E171" s="1">
+        <v>30</v>
+      </c>
+      <c r="F171" s="1">
+        <v>45</v>
+      </c>
+      <c r="G171" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="H171" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="I171" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="J171" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="172" ht="15" spans="1:10">
+      <c r="A172" s="1">
+        <v>171</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C172" s="1"/>
+      <c r="D172" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E172" s="1">
+        <v>46</v>
+      </c>
+      <c r="F172" s="1">
+        <v>93</v>
+      </c>
+      <c r="G172" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H172" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="I172" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="J172" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" ht="15" spans="1:10">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C173" s="1"/>
+      <c r="D173" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E173" s="1">
+        <v>94</v>
+      </c>
+      <c r="F173" s="1">
+        <v>120</v>
+      </c>
+      <c r="G173" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="H173" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="I173" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="J173" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="174" ht="15" spans="1:10">
+      <c r="A174" s="1">
         <v>173</v>
       </c>
-      <c r="C122" s="1"/>
-      <c r="D122" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="E122" s="1">
+      <c r="B174" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C174" s="5"/>
+      <c r="D174" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="E174" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="F174" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="G174" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="H174" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="I174" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="J174" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="175" ht="15" spans="1:10">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C175" s="5"/>
+      <c r="D175" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="E175" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="F175" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="G175" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="H175" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="I175" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="J175" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" ht="15" spans="1:10">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C176" s="5"/>
+      <c r="D176" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="E176" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="F176" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="G176" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H176" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="I176" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="J176" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="177" ht="15" spans="1:10">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C177" s="1"/>
+      <c r="D177" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E177" s="1">
+        <v>140</v>
+      </c>
+      <c r="F177" s="1">
+        <v>159</v>
+      </c>
+      <c r="G177" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="H177" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="I177" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="J177" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="178" ht="15" spans="1:10">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C178" s="1"/>
+      <c r="D178" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E178" s="1">
+        <v>160</v>
+      </c>
+      <c r="F178" s="1">
+        <v>179</v>
+      </c>
+      <c r="G178" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H178" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="I178" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="J178" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" ht="15" spans="1:10">
+      <c r="A179" s="1">
+        <v>178</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C179" s="1"/>
+      <c r="D179" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E179" s="1">
+        <v>180</v>
+      </c>
+      <c r="F179" s="1">
+        <v>210</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="H179" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="I179" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="J179" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180" ht="15" spans="1:10">
+      <c r="A180" s="1">
+        <v>179</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C180" s="1"/>
+      <c r="D180" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="E180" s="1">
+        <v>43</v>
+      </c>
+      <c r="F180" s="1">
+        <v>58</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="H180" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="I180" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="J180" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="181" ht="15" spans="1:10">
+      <c r="A181" s="1">
+        <v>180</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C181" s="1"/>
+      <c r="D181" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="E181" s="1">
+        <v>59</v>
+      </c>
+      <c r="F181" s="1">
+        <v>75</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H181" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="I181" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="J181" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" ht="15" spans="1:10">
+      <c r="A182" s="1">
+        <v>181</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C182" s="1"/>
+      <c r="D182" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="E182" s="1">
         <v>76</v>
       </c>
-      <c r="F122" s="1">
+      <c r="F182" s="1">
         <v>90</v>
       </c>
-      <c r="G122" s="1" t="s">
+      <c r="G182" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="H182" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="I182" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="J182" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="183" ht="15" spans="1:10">
+      <c r="A183" s="1">
+        <v>182</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C183" s="1"/>
+      <c r="D183" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="H183" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="I183" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="J183" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="184" ht="15" spans="1:10">
+      <c r="A184" s="1">
+        <v>183</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C184" s="1"/>
+      <c r="D184" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H184" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="I184" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="J184" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" ht="15" spans="1:10">
+      <c r="A185" s="1">
         <v>184</v>
       </c>
-      <c r="H122" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="I122" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="J122" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10">
-      <c r="A123" s="1">
-        <v>125</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C123" s="1"/>
-      <c r="D123" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="H123" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="I123" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="J123" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10">
-      <c r="A124" s="1">
-        <v>126</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C124" s="1"/>
-      <c r="D124" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="H124" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="I124" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="J124" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10">
-      <c r="A125" s="1">
-        <v>127</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C125" s="1"/>
-      <c r="D125" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H125" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="I125" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="J125" s="1">
+      <c r="B185" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C185" s="1"/>
+      <c r="D185" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="H185" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="I185" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="J185" s="1">
         <v>5</v>
       </c>
     </row>
